--- a/yanfeng/泡泡图DATA/泡泡图历史数据.xlsx
+++ b/yanfeng/泡泡图DATA/泡泡图历史数据.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -591,30 +591,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30032991-EBP</t>
+          <t>30032543-EBP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30032991-2026,AP,Jianghuai,JH-C-mirror,assembly,260009,14T,Equipment</t>
+          <t>30032543-2026,AP,smartmi,F2N-light,assemble,250363,T,Equipment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zhang Shuai27_张帅(uzhas1129)</t>
+          <t>Huang Sheng02_黄圣(uhuas068)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Jianghuai,JH-C-mirror,assembly</t>
+          <t>smartmi,F2N-light,assemble</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -624,7 +628,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>30030795-2026,AP,Jianghuai,JH-A Roller glue,000000,1M,Equipment</t>
+          <t>30031276-2026,AP,smartmi,MX11_Light,auto,000000,1M2T,Equipment</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -633,24 +637,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30032543-EBP</t>
+          <t>30034473-EBP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30032543-2026,AP,smartmi,F2N-light,assemble,250363,T,Equipment</t>
+          <t>30034473-2026,AP,SERES Motors,F2N-light,260081,M,Equipment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Huang Sheng02_黄圣(uhuas068)</t>
+          <t>Hao Xiuxia_郝秀霞(uhaox031)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -660,7 +664,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>smartmi,F2N-light,assemble</t>
+          <t>SERES Motors,F2N-light</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -670,7 +674,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>30031276-2026,AP,smartmi,MX11_Light,auto,000000,1M2T,Equipment</t>
+          <t>30022444-2025,AP,SERES Motors,F3-IP,Vacuum,000000,1M,Equipment</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -679,34 +683,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30034473-EBP</t>
+          <t>30032067-EBP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30034473-2026,AP,SERES Motors,F2N-light,260081,M,Equipment</t>
+          <t>30032067-2025,AP,XPENG,G02顶棚EOL ,250364,1M2T,Equipment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hao Xiuxia_郝秀霞(uhaox031)</t>
+          <t>Huang Sheng02_黄圣(uhuas068)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SERES Motors,F2N-light</t>
+          <t>XPENG,G02顶棚EOL</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -716,7 +720,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>30022444-2025,AP,SERES Motors,F3-IP,Vacuum,000000,1M,Equipment</t>
+          <t>30028120-2025,AP,XPENG,G02_Air Vent,Noise,000000,1T,Equipment</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -725,34 +729,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30032067-EBP</t>
+          <t>30032988-EBP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30032067-2025,AP,XPENG,G02顶棚EOL ,250364,1M2T,Equipment</t>
+          <t>30032988-2026,AP,SERES Motors,V32-mirror,Assembly,260007, 14T,Equipment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Huang Sheng02_黄圣(uhuas068)</t>
+          <t>Guo Xinjie_郭新杰(uguox097)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>XPENG,G02顶棚EOL</t>
+          <t>SERES Motors,V32-mirror,Assembly</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -762,7 +762,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>30028120-2025,AP,XPENG,G02_Air Vent,Noise,000000,1T,Equipment</t>
+          <t>30032590-2026,AP,SERES Motors,V32/K89-IP,Spary,000000,1M,Equipment</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -771,30 +771,38 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30032988-EBP</t>
+          <t>30032531-EBP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30032988-2026,AP,SERES Motors,V32-mirror,Assembly,260007, 14T,Equipment</t>
+          <t>30032531-2026,AP,SERES Motors,F2N-DAB, Lamination, 250383, T,Equipment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guo Xinjie_郭新杰(uguox097)</t>
+          <t>Huang Dongfang01_黄东方(uhuad056)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SERES Motors,V32-mirror,Assembly</t>
+          <t>SERES Motors,F2N-DAB, Lamination,</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -804,29 +812,29 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>30032590-2026,AP,SERES Motors,V32/K89-IP,Spary,000000,1M,Equipment</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>30012870-2023,AP,SERES Motors,F2-DAB,Lamination,000000,1M1T,Equipment</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>30030067-EBP</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30032531-EBP</t>
+          <t>30017125-EBP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30032531-2026,AP,SERES Motors,F2N-DAB, Lamination, 250383, T,Equipment</t>
+          <t>30017125-2024,AP,SERES Motors,F2-DAB,Lamination,220332,M,Equipment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Zou Chengcheng_邹成成(uzouc016)</t>
@@ -834,17 +842,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Huang Dongfang01_黄东方(uhuad056)</t>
+          <t>Kan Chengben_阚城奔(ukanc012)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SERES Motors,F2N-DAB, Lamination,</t>
+          <t>SERES Motors,F2-DAB,Lamination</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -857,44 +865,40 @@
           <t>30012870-2023,AP,SERES Motors,F2-DAB,Lamination,000000,1M1T,Equipment</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>30030067-EBP</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30017125-EBP</t>
+          <t>30032909-EBP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30017125-2024,AP,SERES Motors,F2-DAB,Lamination,220332,M,Equipment</t>
+          <t>30032909-2026,AP,SERES Motors,F2N10lm-light,assemble,260017,T,Equipment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Zou Chengcheng_邹成成(uzouc016)</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kan Chengben_阚城奔(ukanc012)</t>
+          <t>Zhou Liwen_周理文(uzhol008)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SERES Motors,F2-DAB,Lamination</t>
+          <t>SERES Motors,F2N10lm-light,assemble</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -904,7 +908,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30012870-2023,AP,SERES Motors,F2-DAB,Lamination,000000,1M1T,Equipment</t>
+          <t>30028025-2026,AP,SERES Motors,F1L-CNSL,Assembly,000000,1M,Equipment</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -913,44 +917,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>30032909-EBP</t>
+          <t>30034478-EBP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30032909-2026,AP,SERES Motors,F2N10lm-light,assemble,260017,T,Equipment</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>30034478-2026,AP,Toyota,780B-DP, flaming,260080,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zhou Liwen_周理文(uzhol008)</t>
+          <t>Zhang Shuai27_张帅(uzhas1129)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SERES Motors,F2N10lm-light,assemble</t>
+          <t>Toyota,780B-DP,flaming</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>100</v>
       </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>0.134</v>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>30028025-2026,AP,SERES Motors,F1L-CNSL,Assembly,000000,1M,Equipment</t>
+          <t>1F001051-2023,AP,Toyota,920B,Equipment</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -959,66 +969,66 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>30033373-EBP</t>
+          <t>30033404-EBP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30033373-2026,AP,Huawei Anhui,F03F05,Assembly,260030,T,Equipment</t>
+          <t>30033404-2026,AP,VW Group,VW426-DP,Lamination,260033,M,Equipment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>赵凯亮</t>
+          <t>路公超</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Meng Zibing_孟子冰(umenz002)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Huawei Anhui,F03F05,Assembly</t>
+          <t>VW Group,VW426-DP,Lamination</t>
         </is>
       </c>
       <c r="I12" t="n">
         <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="K12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>30032261-2026,AP,Huawei Anhui,F03F05,Assembly,000000,1m1T,Equipment</t>
-        </is>
-      </c>
+        <v>0.169</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>30033376-EBP</t>
+          <t>30033407-EBP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>30033376-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260031,T,Equipment</t>
+          <t>30033407-2026,AP,Huawei Anhui,F05/F03 CNSL,Assembly,260036,M,Equipment</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1028,7 +1038,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1039,98 +1049,90 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Huawei Anhui,F05&amp;F03,Assembly</t>
+          <t>Huawei Anhui,F05/F03 CNSL,Assembly</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J13" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="K13" t="n">
         <v>0.05</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>30032261-2026,AP,Huawei Anhui,F03F05,Assembly,000000,1m1T,Equipment</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>30034747-EBP</t>
+          <t>30032370-EBP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30034747-2026,AP,Huawei Anhui,X90-DP,260116,Glue spray,M,Equipment</t>
+          <t>30032370-2026,AP,SERES Motors,F3_Seat rail,Assy,250379,Equipment</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>路公超</t>
+          <t>赵凯亮</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
+          <t>Yang Yang28_杨阳(uyany430)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cheng Debao_程德宝(uched025)</t>
+          <t>Huang Dinghui_黄定辉(uhuad002)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Huawei Anhui,X90-DP,260116</t>
+          <t>SERES Motors,F3_Seat rail</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>100</v>
       </c>
       <c r="J14" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="K14" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>30030766-2025,AP,Huawei Anhui,EHV_DP,Lami,000000,4T,Equipment</t>
-        </is>
-      </c>
+        <v>0.334</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>30033407-EBP</t>
+          <t>30035089-EBP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>30033407-2026,AP,Huawei Anhui,F05/F03 CNSL,Assembly,260036,M,Equipment</t>
+          <t>30035089-2026,AP,SAIC-GM,E2LB-2-IP, Automation, 260129, M,Equipment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1140,39 +1142,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Meng Zibing_孟子冰(umenz002)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Wang Xiaoyu03_王晓宇(uwanx1357)</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Huawei Anhui,F05/F03 CNSL,Assembly</t>
+          <t>SAIC-GM,E2LB-2-IP,Automation</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J15" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="K15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>30032261-2026,AP,Huawei Anhui,F03F05,Assembly,000000,1m1T,Equipment</t>
-        </is>
-      </c>
+        <v>0.075</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
     </row>
@@ -1226,23 +1228,19 @@
       <c r="K16" t="n">
         <v>0.091</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>30027367-2025,AP,BYD,SA3-DP Lam&amp;Wrapping,000000.2M,Equipment</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>30035089-EBP</t>
+          <t>30033376-EBP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30035089-2026,AP,SAIC-GM,E2LB-2-IP, Automation, 260129, M,Equipment</t>
+          <t>30033376-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260031,T,Equipment</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1252,27 +1250,23 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zou Chengcheng_邹成成(uzouc016)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Wang Xiaoyu03_王晓宇(uwanx1357)</t>
-        </is>
-      </c>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SAIC-GM,E2LB-2-IP,Automation</t>
+          <t>Huawei Anhui,F05&amp;F03,Assembly</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1282,13 +1276,9 @@
         <v>-9</v>
       </c>
       <c r="K17" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>30034773-2027,AP,SAIC-GM,E2LB-2-IP,Automation,000000,1M,Equipment</t>
-        </is>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
     </row>
@@ -1338,11 +1328,7 @@
       <c r="K18" t="n">
         <v>0.05</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>30032261-2026,AP,Huawei Anhui,F03F05,Assembly,000000,1m1T,Equipment</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
     </row>
@@ -1396,41 +1382,41 @@
       <c r="K19" t="n">
         <v>0.001</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>30032880-2026,AP,BYD,广州，Roll rubber,000000,1M,Equipment</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>30033405-EBP</t>
+          <t>30034747-EBP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30033405-2026,AP,Huawei Anhui,F05 IP,Assembly,260038,M,Equipment</t>
+          <t>30034747-2026,AP,Huawei Anhui,X90-DP,260116,Glue spray,M,Equipment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>赵凯亮</t>
+          <t>路公超</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Meng Zibing_孟子冰(umenz002)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Cheng Debao_程德宝(uched025)</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>2026-05-31</t>
@@ -1438,93 +1424,85 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Huawei Anhui,F05 IP,Assembly</t>
+          <t>Huawei Anhui,X90-DP,260116</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J20" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>30032261-2026,AP,Huawei Anhui,F03F05,Assembly,000000,1m1T,Equipment</t>
-        </is>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>30033404-EBP</t>
+          <t>30032706-EBP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>30033404-2026,AP,VW Group,VW426-DP,Lamination,260033,M,Equipment</t>
+          <t>30032706-2025,AP,SERES Motors,A15-mirror, assy, 260006, 15T,Equipment</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>路公超</t>
+          <t>赵凯亮</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Huang Linjian_黄琳健(uhual254)</t>
+          <t>Wang Wanfang_王万芳(uwanw356)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>VW Group,VW426-DP,Lamination</t>
+          <t>SERES Motors,A15-mirror,assy</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>100</v>
       </c>
       <c r="J21" t="n">
-        <v>-4</v>
+        <v>-16</v>
       </c>
       <c r="K21" t="n">
-        <v>0.169</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>30019456-2025,AP,VW Group,VW426-IP,Auto cell,000000,1M,Equipment</t>
-        </is>
-      </c>
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>30032370-EBP</t>
+          <t>30033373-EBP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>30032370-2026,AP,SERES Motors,F3_Seat rail,Assy,250379,Equipment</t>
+          <t>30033373-2026,AP,Huawei Anhui,F03F05,Assembly,260030,T,Equipment</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1534,55 +1512,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Yang Yang28_杨阳(uyany430)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Huang Dinghui_黄定辉(uhuad002)</t>
-        </is>
-      </c>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SERES Motors,F3_Seat rail</t>
+          <t>Huawei Anhui,F03F05,Assembly</t>
         </is>
       </c>
       <c r="I22" t="n">
         <v>100</v>
       </c>
       <c r="J22" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="K22" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>30030599-2026,AP,SERES Motors,F3_Seat rail,Assy,000000,1M,Equipment</t>
-        </is>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>30032706-EBP</t>
+          <t>30033405-EBP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30032706-2025,AP,SERES Motors,A15-mirror, assy, 260006, 15T,Equipment</t>
+          <t>30033405-2026,AP,Huawei Anhui,F05 IP,Assembly,260038,M,Equipment</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1592,19 +1562,15 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Wang Wanfang_王万芳(uwanw356)</t>
-        </is>
-      </c>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>2026-05-31</t>
@@ -1612,25 +1578,1343 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SERES Motors,A15-mirror,assy</t>
+          <t>Huawei Anhui,F05 IP,Assembly</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J23" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="K23" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>30029682-2026,AP,SERES Motors,A15-Other,Assembly,000000,1M,Equipment</t>
-        </is>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>30035161-EBP</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>30035161-2026,AP,BJEV,X90,Lamination,260132,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>路公超</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>BJEV,X90,Lamination</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>100</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>30033569-2026,AP,BJEV,X90_IP,Laser,000000,1T,Equipment</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>30034168-EBP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>30034168-2026,AP,SVW,A-SUV-mirror,assembly,260008,15T,Equipment</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Zhou Liwen_周理文(uzhol008)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SVW,A-SUV-mirror,assembly</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>100</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>30031258-2025,AP,SVW,VW Bsuv,vanity mirror,000000,1M1,Equipment</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>30034166-EBP</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>30034166-2026,AP,SAIC-GM,C1UL-2,CNSL,Lamination,260073,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>路公超</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>SAIC-GM,C1UL-2,CNSL,Lamination</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>90</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-15</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>30033571-2026,AP,SAIC-GM,C1UL-2_CNSL,Lami,000000,2T,Equipment</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>30034746-EBP</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>30034746-2026,AP,Huawei Anhui,X90-DP,260115,glue spray,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>路公超</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Cheng Debao_程德宝(uched025)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Huawei Anhui,X90-DP,260115</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>100</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>30030766-2025,AP,Huawei Anhui,EHV_DP,Lami,000000,4T,Equipment</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>30035325-EBP</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>30035325-2026,AP,SERES Motors,遮阳板,1200压机,260145,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>路公超</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>SERES Motors,遮阳板,1200压机</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>100</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>30035225-2026,AP,SERES Motors,遮阳板1200压机,000000,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>30034480-EBP</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>路公超</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Chen Ziyi01_陈子翌(uchez443)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Toyota,780B,Spraying</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>90</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1F001051-2023,AP,Toyota,920B,Equipment</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>30029284-EBP</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>30029284-2026,AP,SAIC-VW,VW316-9-IP,Automation,250219,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Xia Yang_夏阳(uxiay057)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Hao Xiuxia_郝秀霞(uhaox031)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>SAIC-VW,VW316-9-IP,Automation</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>100</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-15</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>30027751-2025,AP,SAIC-VW,VW316-9IP,Automation,000000,1M2T,Equipment</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30033461-EBP</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>30033461-2026,AP,SVW,B-SUV-mirror,assy,260041,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>SVW,B-SUV-mirror,assy</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>90</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>30031258-2025,AP,SVW,VW Bsuv,vanity mirror,000000,1M1,Equipment</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>30034477-EBP</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>30034477-2025,AP,Toyota,780B-DP,Flaming, 260079,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Toyota,780B-DP,Flaming</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>100</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-14</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1F001051-2023,AP,Toyota,920B,Equipment</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>30033409-EBP</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>30033409-2026,AP,Huawei Anhui,F05/F03 CNSL,Assembly,260037,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Huawei Anhui,F05/F03 CNSL,Assembly</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>100</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>30032261-2026,AP,Huawei Anhui,F03F05,Assembly,000000,1m1T,Equipment</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>30031537-EBP</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>30031537-2026,AP,Huawei Anhui,EHV-DP,Lamination,250338,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>路公超</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Xia Yang_夏阳(uxiay057)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Huawei Anhui,EHV-DP,Lamination</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>90</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>30030766-2025,AP,Huawei Anhui,EHV_DP,Lami,000000,4T,Equipment</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>30030761-EBP</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>30030761-2025,AP,SAIC-VW,VW416-IP,Automatin,250306,M,,Equipment</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Xia Yang_夏阳(uxiay057)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Liu Jinghua01_刘璟华(uliuj595)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>SAIC-VW,VW416-IP,Automatin,250306</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>100</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>30027751-2025,AP,SAIC-VW,VW316-9IP,Automation,000000,1M2T,Equipment</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>30035209-EBP</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>30035209-2026,AP,Jianghuai,C673-DP,Foam sticking,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Jianghuai,C673-DP</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>100</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>30030795-2026,AP,Jianghuai,JH-A Roller glue,000000,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>30034615-EBP</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>30034615-2026,AP,BYD,MR&amp;ST-IP, Glue,260091, M,Equipment</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>路公超</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Yuan Shuai_袁帅(uyuas003)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>BYD,MR&amp;ST-IP,Glue</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>90</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>30017103-2024,AP,BYD,BYD MR-IP,Prefixture,000000,2T,Equipment</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>30033578-EBP</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>30033578-2026,AP,Tes,TBD_Click Rim, Lami, 260050, T,Equipment</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>路公超</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Zhou Huasheng_周华盛(uzhoh176)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Tes,TBD_Click Rim,Lami</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>100</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>30028949-2026,AP,Tes,TBD_Click RIM,Lami,000000,1T,Equipment</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>30034171-EBP</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>30034171-2026,AP,Jianghuai,JHC-sun visor,assy, 260074, NT,Equipment</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Jianghuai,JHC-sun visor,assy</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>100</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>30030795-2026,AP,Jianghuai,JH-A Roller glue,000000,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>30033723-EBP</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>30033723-2026,AP,VW Group,VW426 PAB Chute Cell CI,260042,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Wei Shaoguan_韦少官(uweis086)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>VW Group,VW426 PAB Chute Cell CI</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>90</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>30019456-2025,AP,VW Group,VW426-IP,Auto cell,000000,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>30031541-EBP</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>30031541-2026,AP,Huawei Anhui,EHV-DP,Lamination,250340,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>路公超</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Xia Yang_夏阳(uxiay057)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Huawei Anhui,EHV-DP,Lamination</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>100</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>30030766-2025,AP,Huawei Anhui,EHV_DP,Lami,000000,4T,Equipment</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>30031540-EBP</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>30031540-2026,AP,Huawei Anhui,EHV-DP,Lamination,250339,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>路公超</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Xia Yang_夏阳(uxiay057)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Huawei Anhui,EHV-DP,Lamination</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>100</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>30030766-2025,AP,Huawei Anhui,EHV_DP,Lami,000000,4T,Equipment</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>30032991-EBP</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>30032991-2026,AP,Jianghuai,JH-C-mirror,assembly,260009,14T,Equipment</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Zhang Shuai27_张帅(uzhas1129)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Jianghuai,JH-C-mirror,assembly</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>90</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>30030795-2026,AP,Jianghuai,JH-A Roller glue,000000,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>30035208-EBP</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>30035208-2026,AP,Jianghuai,C673-DP,Foam Sticking,260140,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Jianghuai,C673-DP,Foam Sticking</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>100</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>30030795-2026,AP,Jianghuai,JH-A Roller glue,000000,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>30031304-EBP</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>30031304-2026,AP,Chery,EHV-Pilla,Welding,250319,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Xia Yang_夏阳(uxiay057)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Huang Sheng02_黄圣(uhuas068)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Chery,EHV-Pilla,Welding</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>100</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-16</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>30030391-2026,AP,Chery,EHV-Pillar,Welding,000000,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>30029921-EBP</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>30029921-2026,AP,Tes,Highland-FC, Assembly,250246,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>赵凯亮</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Li Yanchen_李彦辰(ulixy466)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Tes,Highland-FC,Assembly</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>100</v>
+      </c>
+      <c r="J46" t="n">
+        <v>-26</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>30028749-2025,AP,Tes,Highland-FC,Trans MX,000000,1M9T,Equipment</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
